--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_hoog.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_hoog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Zone</t>
   </si>
@@ -28,7 +28,10 @@
     <t>OV</t>
   </si>
   <si>
-    <t>Auto-FietsOV_Fiets</t>
+    <t>Auto-Fiets</t>
+  </si>
+  <si>
+    <t>OV_Fiets</t>
   </si>
   <si>
     <t>Auto_OV</t>
@@ -391,6 +394,9 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2">

--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_hoog.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_hoog.xlsx
@@ -8365,7 +8365,7 @@
         <v>0.6295914745525416</v>
       </c>
       <c r="D308">
-        <v>0.3969067150793356</v>
+        <v>0.3969067150793357</v>
       </c>
       <c r="E308">
         <v>0.6192707555199289</v>
@@ -8391,7 +8391,7 @@
         <v>0.8453350043963259</v>
       </c>
       <c r="D309">
-        <v>0.6576752455461131</v>
+        <v>0.6576752455461132</v>
       </c>
       <c r="E309">
         <v>0.8383937412403915</v>
